--- a/Diplomka/stability-tests/results/errors_table.xlsx
+++ b/Diplomka/stability-tests/results/errors_table.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="520" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="718" uniqueCount="26">
   <si>
     <t>Row</t>
   </si>
@@ -139,21 +139,21 @@
   <dimension ref="A1:O10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.3828125" customWidth="true"/>
-    <col min="2" max="2" width="15.61328125" customWidth="true"/>
-    <col min="3" max="3" width="16" customWidth="true"/>
-    <col min="4" max="4" width="15.61328125" customWidth="true"/>
-    <col min="5" max="5" width="16" customWidth="true"/>
-    <col min="6" max="6" width="15.61328125" customWidth="true"/>
-    <col min="7" max="7" width="15.61328125" customWidth="true"/>
-    <col min="8" max="8" width="15.61328125" customWidth="true"/>
-    <col min="9" max="9" width="15.61328125" customWidth="true"/>
-    <col min="10" max="10" width="15.61328125" customWidth="true"/>
-    <col min="11" max="11" width="16" customWidth="true"/>
-    <col min="12" max="12" width="16" customWidth="true"/>
-    <col min="13" max="13" width="16" customWidth="true"/>
-    <col min="14" max="14" width="15.61328125" customWidth="true"/>
-    <col min="15" max="15" width="6.53515625" customWidth="true"/>
+    <col min="1" max="1" width="6.28515625" customWidth="true"/>
+    <col min="2" max="2" width="15.5703125" customWidth="true"/>
+    <col min="3" max="3" width="15.5703125" customWidth="true"/>
+    <col min="4" max="4" width="15.5703125" customWidth="true"/>
+    <col min="5" max="5" width="15.5703125" customWidth="true"/>
+    <col min="6" max="6" width="15.5703125" customWidth="true"/>
+    <col min="7" max="7" width="15.5703125" customWidth="true"/>
+    <col min="8" max="8" width="15.5703125" customWidth="true"/>
+    <col min="9" max="9" width="15.5703125" customWidth="true"/>
+    <col min="10" max="10" width="15.5703125" customWidth="true"/>
+    <col min="11" max="11" width="15.5703125" customWidth="true"/>
+    <col min="12" max="12" width="15.5703125" customWidth="true"/>
+    <col min="13" max="13" width="15.5703125" customWidth="true"/>
+    <col min="14" max="14" width="15.5703125" customWidth="true"/>
+    <col min="15" max="15" width="6.5703125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -208,43 +208,37 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>75.236022452141071</v>
+        <v>5.2377593063382642e-08</v>
       </c>
       <c r="C2" s="0">
-        <v>27.616217573695241</v>
+        <v>2.0868317046900098e-07</v>
       </c>
       <c r="D2" s="0">
-        <v>54.02297974301564</v>
+        <v>3.0939957074794876e-08</v>
       </c>
       <c r="E2" s="0">
-        <v>67.292159185234667</v>
+        <v>4.7845404990238133e-08</v>
       </c>
       <c r="F2" s="0">
-        <v>-144.64269012751535</v>
+        <v>2.7539166034097848e-07</v>
       </c>
       <c r="G2" s="0">
-        <v>68.703152514967186</v>
+        <v>1.7023840283462513e-07</v>
       </c>
       <c r="H2" s="0">
-        <v>-134.26606192722858</v>
-      </c>
-      <c r="I2" s="0">
-        <v>-149.68666975686992</v>
-      </c>
-      <c r="J2" s="0">
-        <v>40.826333508499623</v>
-      </c>
-      <c r="K2" s="0">
-        <v>60.309164244892699</v>
-      </c>
+        <v>2.6843230854463613e-07</v>
+      </c>
+      <c r="I2" s="0"/>
+      <c r="J2" s="0"/>
+      <c r="K2" s="0"/>
       <c r="L2" s="0">
-        <v>-3.458939258916776</v>
+        <v>1.5055835675966519e-07</v>
       </c>
       <c r="M2" s="0">
-        <v>75.236022452141071</v>
+        <v>2.7539166034097848e-07</v>
       </c>
       <c r="N2" s="0">
-        <v>-149.68666975686992</v>
+        <v>3.0939957074794876e-08</v>
       </c>
       <c r="O2" s="0" t="s">
         <v>22</v>
@@ -255,43 +249,37 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>29.952836113559496</v>
+        <v>3.5045436855652646e-07</v>
       </c>
       <c r="C3" s="0">
-        <v>4.4141416205244282</v>
+        <v>1.8482735733134093e-07</v>
       </c>
       <c r="D3" s="0">
-        <v>164.88550853516668</v>
+        <v>4.1129506415799321e-10</v>
       </c>
       <c r="E3" s="0">
-        <v>157.50286313597874</v>
+        <v>1.4518611661924518e-07</v>
       </c>
       <c r="F3" s="0">
-        <v>141.36124141963521</v>
+        <v>3.5645146855021897e-07</v>
       </c>
       <c r="G3" s="0">
-        <v>-146.13166161169332</v>
+        <v>8.6694964155852724e-08</v>
       </c>
       <c r="H3" s="0">
-        <v>174.66079364520567</v>
-      </c>
-      <c r="I3" s="0">
-        <v>-12.019448861865104</v>
-      </c>
-      <c r="J3" s="0">
-        <v>-147.29849491346394</v>
-      </c>
-      <c r="K3" s="0">
-        <v>156.99823830938951</v>
-      </c>
+        <v>6.1897731684776672e-08</v>
+      </c>
+      <c r="I3" s="0"/>
+      <c r="J3" s="0"/>
+      <c r="K3" s="0"/>
       <c r="L3" s="0">
-        <v>52.432601739243736</v>
+        <v>1.69417614566017e-07</v>
       </c>
       <c r="M3" s="0">
-        <v>174.66079364520567</v>
+        <v>3.5645146855021897e-07</v>
       </c>
       <c r="N3" s="0">
-        <v>-147.29849491346394</v>
+        <v>4.1129506415799321e-10</v>
       </c>
       <c r="O3" s="0" t="s">
         <v>22</v>
@@ -302,43 +290,43 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>4.3938507284609337e-05</v>
+        <v>1.0427847289021148e-07</v>
       </c>
       <c r="C4" s="0">
-        <v>0.00040646968987319157</v>
+        <v>1.9983753269447248e-07</v>
       </c>
       <c r="D4" s="0">
-        <v>1.3201354947228528e-05</v>
+        <v>3.8805392086176445e-08</v>
       </c>
       <c r="E4" s="0">
-        <v>0.00020453344118782197</v>
+        <v>8.1678294319729281e-08</v>
       </c>
       <c r="F4" s="0">
-        <v>4.3187480048710647e-05</v>
+        <v>1.0700273939455957e-07</v>
       </c>
       <c r="G4" s="0">
-        <v>0.00020845680199299121</v>
+        <v>4.3328669740575336e-09</v>
       </c>
       <c r="H4" s="0">
-        <v>2.8911204694121707e-05</v>
+        <v>5.9124717251830949e-08</v>
       </c>
       <c r="I4" s="0">
-        <v>0.00032891222002182573</v>
+        <v>2.8044072383072876e-08</v>
       </c>
       <c r="J4" s="0">
-        <v>2.2387867812359972e-06</v>
+        <v>1.3269475443493819e-09</v>
       </c>
       <c r="K4" s="0">
-        <v>0.00018798159456801916</v>
+        <v>2.2494318502017288e-08</v>
       </c>
       <c r="L4" s="0">
-        <v>0.00014678310813997559</v>
+        <v>6.4692535404047715e-08</v>
       </c>
       <c r="M4" s="0">
-        <v>0.00040646968987319157</v>
+        <v>1.9983753269447248e-07</v>
       </c>
       <c r="N4" s="0">
-        <v>2.2387867812359972e-06</v>
+        <v>1.3269475443493819e-09</v>
       </c>
       <c r="O4" s="0" t="s">
         <v>22</v>
@@ -349,43 +337,43 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>0.0042355184754618389</v>
+        <v>5.6655271899861152e-08</v>
       </c>
       <c r="C5" s="0">
-        <v>1.474501397907559e-08</v>
+        <v>1.4744098190992232e-08</v>
       </c>
       <c r="D5" s="0">
-        <v>1.3850667617172645e-07</v>
+        <v>1.3850703110742815e-07</v>
       </c>
       <c r="E5" s="0">
-        <v>2.7623266214990998e-08</v>
+        <v>2.762635792105789e-08</v>
       </c>
       <c r="F5" s="0">
-        <v>0.0016598044610400982</v>
+        <v>6.3100566555879326e-08</v>
       </c>
       <c r="G5" s="0">
-        <v>5.3195692435664471e-08</v>
+        <v>5.3122564121632527e-08</v>
       </c>
       <c r="H5" s="0">
-        <v>0.0042715941758084</v>
+        <v>4.824833382309571e-08</v>
       </c>
       <c r="I5" s="0">
-        <v>5.9298923028738599e-09</v>
+        <v>5.9228950497709421e-09</v>
       </c>
       <c r="J5" s="0">
-        <v>3.8218447435767282e-08</v>
+        <v>3.8218843520048801e-08</v>
       </c>
       <c r="K5" s="0">
-        <v>2.3924279418271447e-07</v>
+        <v>2.3925801900093354e-07</v>
       </c>
       <c r="L5" s="0">
-        <v>0.0010167434574093063</v>
+        <v>6.8540398119070033e-08</v>
       </c>
       <c r="M5" s="0">
-        <v>0.0042715941758084</v>
+        <v>2.3925801900093354e-07</v>
       </c>
       <c r="N5" s="0">
-        <v>5.9298923028738599e-09</v>
+        <v>5.9228950497709421e-09</v>
       </c>
       <c r="O5" s="0" t="s">
         <v>22</v>
@@ -396,43 +384,43 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>5.8008374643881167e-08</v>
+        <v>5.8008335499201564e-08</v>
       </c>
       <c r="C6" s="0">
-        <v>1.8378016617728203e-07</v>
+        <v>1.8377984387836301e-07</v>
       </c>
       <c r="D6" s="0">
-        <v>2.5565954765660888e-08</v>
+        <v>2.5565690942022546e-08</v>
       </c>
       <c r="E6" s="0">
-        <v>5.6122938206133838e-08</v>
+        <v>5.6123097230566723e-08</v>
       </c>
       <c r="F6" s="0">
-        <v>6.9308809894773244e-08</v>
+        <v>6.9308475242484003e-08</v>
       </c>
       <c r="G6" s="0">
-        <v>3.1879194158270516e-07</v>
+        <v>3.1879294703166178e-07</v>
       </c>
       <c r="H6" s="0">
-        <v>4.5327721999386104e-08</v>
+        <v>4.5327835305157203e-08</v>
       </c>
       <c r="I6" s="0">
-        <v>2.7603299860091146e-08</v>
+        <v>2.760328255372432e-08</v>
       </c>
       <c r="J6" s="0">
-        <v>1.3830791006456078e-08</v>
+        <v>1.3830186157624925e-08</v>
       </c>
       <c r="K6" s="0">
-        <v>1.6843540811789849e-08</v>
+        <v>1.6844701461476193e-08</v>
       </c>
       <c r="L6" s="0">
-        <v>8.1518353894815954e-08</v>
+        <v>8.1518439530228219e-08</v>
       </c>
       <c r="M6" s="0">
-        <v>3.1879194158270516e-07</v>
+        <v>3.1879294703166178e-07</v>
       </c>
       <c r="N6" s="0">
-        <v>1.3830791006456078e-08</v>
+        <v>1.3830186157624925e-08</v>
       </c>
       <c r="O6" s="0" t="s">
         <v>22</v>
@@ -443,43 +431,43 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>3.6088587017458656e-08</v>
+        <v>3.6087785032808391e-08</v>
       </c>
       <c r="C7" s="0">
-        <v>2.5557808822534029e-08</v>
+        <v>2.5558034793398719e-08</v>
       </c>
       <c r="D7" s="0">
-        <v>4.67729770199359e-08</v>
+        <v>4.6773837858091323e-08</v>
       </c>
       <c r="E7" s="0">
-        <v>3.7532650095604334e-08</v>
+        <v>3.7532824396501026e-08</v>
       </c>
       <c r="F7" s="0">
-        <v>2.4313190500296362e-07</v>
+        <v>2.4313246512467687e-07</v>
       </c>
       <c r="G7" s="0">
-        <v>1.9890721584958387e-07</v>
+        <v>1.989069387651088e-07</v>
       </c>
       <c r="H7" s="0">
-        <v>1.3369331909132582e-07</v>
+        <v>1.3369309175756598e-07</v>
       </c>
       <c r="I7" s="0">
-        <v>29.072582140905606</v>
+        <v>22.52421208182524</v>
       </c>
       <c r="J7" s="0">
-        <v>39.675731537644921</v>
+        <v>28.405601388921397</v>
       </c>
       <c r="K7" s="0">
-        <v>33.145570013754998</v>
+        <v>24.894234190691215</v>
       </c>
       <c r="L7" s="0">
-        <v>10.189388441398998</v>
+        <v>7.5824048383122831</v>
       </c>
       <c r="M7" s="0">
-        <v>39.675731537644921</v>
+        <v>28.405601388921397</v>
       </c>
       <c r="N7" s="0">
-        <v>2.5557808822534029e-08</v>
+        <v>2.5558034793398719e-08</v>
       </c>
       <c r="O7" s="0" t="s">
         <v>22</v>
@@ -490,43 +478,43 @@
         <v>23</v>
       </c>
       <c r="B8" s="0">
-        <v>0.049102441259491952</v>
+        <v>5.4657056887603545e-08</v>
       </c>
       <c r="C8" s="0">
-        <v>2.2932582366192495e-07</v>
+        <v>2.292852526458309e-07</v>
       </c>
       <c r="D8" s="0">
-        <v>1.4422972294382905e-07</v>
+        <v>1.4422366159831951e-07</v>
       </c>
       <c r="E8" s="0">
-        <v>1.4125097505384192e-08</v>
+        <v>1.4053141840567079e-08</v>
       </c>
       <c r="F8" s="0">
-        <v>7.1653619029640128</v>
+        <v>6.6844074884073317</v>
       </c>
       <c r="G8" s="0">
-        <v>47.407372002536704</v>
+        <v>32.160787715873226</v>
       </c>
       <c r="H8" s="0">
-        <v>90.325337307225666</v>
+        <v>47.432139274977011</v>
       </c>
       <c r="I8" s="0">
-        <v>66.919554723543328</v>
+        <v>40.090901772554531</v>
       </c>
       <c r="J8" s="0">
-        <v>51.698274952689736</v>
+        <v>34.079672276308457</v>
       </c>
       <c r="K8" s="0">
-        <v>50.729351367309086</v>
+        <v>33.655920964885546</v>
       </c>
       <c r="L8" s="0">
-        <v>31.429435508520875</v>
+        <v>19.410382993522521</v>
       </c>
       <c r="M8" s="0">
-        <v>90.325337307225666</v>
+        <v>47.432139274977011</v>
       </c>
       <c r="N8" s="0">
-        <v>1.4125097505384192e-08</v>
+        <v>1.4053141840567079e-08</v>
       </c>
       <c r="O8" s="0" t="s">
         <v>22</v>
@@ -537,43 +525,43 @@
         <v>24</v>
       </c>
       <c r="B9" s="0">
-        <v>47.813380566111853</v>
+        <v>4.8147434975689602e-08</v>
       </c>
       <c r="C9" s="0">
-        <v>1.5484503894146324</v>
+        <v>2.3964324124802145e-08</v>
       </c>
       <c r="D9" s="0">
-        <v>95.057804405346474</v>
+        <v>6.3523335129121971e-08</v>
       </c>
       <c r="E9" s="0">
-        <v>8.5232457599019735</v>
+        <v>9.3906668873093314e-08</v>
       </c>
       <c r="F9" s="0">
-        <v>12.120963435592893</v>
+        <v>2.4464568137978799e-07</v>
       </c>
       <c r="G9" s="0">
-        <v>27.512365144396068</v>
+        <v>8.9239690571560069e-08</v>
       </c>
       <c r="H9" s="0">
-        <v>44.572428114292414</v>
+        <v>1.0319707373368882e-07</v>
       </c>
       <c r="I9" s="0">
-        <v>128.54398000425985</v>
+        <v>3.665395739581638e-08</v>
       </c>
       <c r="J9" s="0">
-        <v>205.79499215139404</v>
+        <v>9.4505582682096381e-08</v>
       </c>
       <c r="K9" s="0">
-        <v>173.12089795018062</v>
+        <v>2.5509755488615571e-08</v>
       </c>
       <c r="L9" s="0">
-        <v>74.460850792089076</v>
+        <v>8.2329350435427221e-08</v>
       </c>
       <c r="M9" s="0">
-        <v>205.79499215139404</v>
+        <v>2.4464568137978799e-07</v>
       </c>
       <c r="N9" s="0">
-        <v>1.5484503894146324</v>
+        <v>2.3964324124802145e-08</v>
       </c>
       <c r="O9" s="0" t="s">
         <v>22</v>
@@ -584,43 +572,43 @@
         <v>25</v>
       </c>
       <c r="B10" s="0">
-        <v>58.090984532763656</v>
+        <v>138.61701699003291</v>
       </c>
       <c r="C10" s="0">
-        <v>48.87016951429824</v>
+        <v>95.580614235520841</v>
       </c>
       <c r="D10" s="0">
-        <v>58.198638417944096</v>
+        <v>139.25330066000532</v>
       </c>
       <c r="E10" s="0">
-        <v>53.061692096730425</v>
+        <v>113.04595929755705</v>
       </c>
       <c r="F10" s="0">
-        <v>53.41259894518474</v>
+        <v>114.665558937436</v>
       </c>
       <c r="G10" s="0">
-        <v>51.338974861543399</v>
+        <v>105.50471422942582</v>
       </c>
       <c r="H10" s="0">
-        <v>57.489873329557781</v>
+        <v>135.24709922674776</v>
       </c>
       <c r="I10" s="0">
-        <v>51.725125784509594</v>
+        <v>107.14717358580023</v>
       </c>
       <c r="J10" s="0">
-        <v>49.986739031864829</v>
+        <v>99.948654708966103</v>
       </c>
       <c r="K10" s="0">
-        <v>49.414840177739961</v>
+        <v>97.686463069026658</v>
       </c>
       <c r="L10" s="0">
-        <v>53.158963669213676</v>
+        <v>114.66965549405185</v>
       </c>
       <c r="M10" s="0">
-        <v>58.198638417944096</v>
+        <v>139.25330066000532</v>
       </c>
       <c r="N10" s="0">
-        <v>48.87016951429824</v>
+        <v>95.580614235520841</v>
       </c>
       <c r="O10" s="0" t="s">
         <v>22</v>

--- a/Diplomka/stability-tests/results/errors_table.xlsx
+++ b/Diplomka/stability-tests/results/errors_table.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="718" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="817" uniqueCount="26">
   <si>
     <t>Row</t>
   </si>

--- a/Diplomka/stability-tests/results/errors_table.xlsx
+++ b/Diplomka/stability-tests/results/errors_table.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="817" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="850" uniqueCount="26">
   <si>
     <t>Row</t>
   </si>

--- a/Diplomka/stability-tests/results/errors_table.xlsx
+++ b/Diplomka/stability-tests/results/errors_table.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="850" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1006" uniqueCount="29">
   <si>
     <t>Row</t>
   </si>
@@ -91,6 +91,15 @@
   </si>
   <si>
     <t>Test 9</t>
+  </si>
+  <si>
+    <t>Test 10</t>
+  </si>
+  <si>
+    <t>Test 11</t>
+  </si>
+  <si>
+    <t>Test 12</t>
   </si>
 </sst>
 </file>
@@ -136,24 +145,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" customWidth="true"/>
-    <col min="2" max="2" width="15.5703125" customWidth="true"/>
-    <col min="3" max="3" width="15.5703125" customWidth="true"/>
-    <col min="4" max="4" width="15.5703125" customWidth="true"/>
-    <col min="5" max="5" width="15.5703125" customWidth="true"/>
-    <col min="6" max="6" width="15.5703125" customWidth="true"/>
-    <col min="7" max="7" width="15.5703125" customWidth="true"/>
-    <col min="8" max="8" width="15.5703125" customWidth="true"/>
-    <col min="9" max="9" width="15.5703125" customWidth="true"/>
-    <col min="10" max="10" width="15.5703125" customWidth="true"/>
-    <col min="11" max="11" width="15.5703125" customWidth="true"/>
-    <col min="12" max="12" width="15.5703125" customWidth="true"/>
-    <col min="13" max="13" width="15.5703125" customWidth="true"/>
-    <col min="14" max="14" width="15.5703125" customWidth="true"/>
-    <col min="15" max="15" width="6.5703125" customWidth="true"/>
+    <col min="1" max="1" width="7.3828125" customWidth="true"/>
+    <col min="2" max="2" width="15.61328125" customWidth="true"/>
+    <col min="3" max="3" width="15.61328125" customWidth="true"/>
+    <col min="4" max="4" width="15.61328125" customWidth="true"/>
+    <col min="5" max="5" width="15.61328125" customWidth="true"/>
+    <col min="6" max="6" width="15.61328125" customWidth="true"/>
+    <col min="7" max="7" width="15.61328125" customWidth="true"/>
+    <col min="8" max="8" width="15.61328125" customWidth="true"/>
+    <col min="9" max="9" width="15.61328125" customWidth="true"/>
+    <col min="10" max="10" width="15.61328125" customWidth="true"/>
+    <col min="11" max="11" width="15.61328125" customWidth="true"/>
+    <col min="12" max="12" width="15.61328125" customWidth="true"/>
+    <col min="13" max="13" width="15.61328125" customWidth="true"/>
+    <col min="14" max="14" width="15.61328125" customWidth="true"/>
+    <col min="15" max="15" width="6.53515625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -572,45 +581,184 @@
         <v>25</v>
       </c>
       <c r="B10" s="0">
-        <v>138.61701699003291</v>
+        <v>3.0834296522909978e-07</v>
       </c>
       <c r="C10" s="0">
-        <v>95.580614235520841</v>
+        <v>2.5514167212623795e-07</v>
       </c>
       <c r="D10" s="0">
-        <v>139.25330066000532</v>
+        <v>8.99417632551304e-08</v>
       </c>
       <c r="E10" s="0">
-        <v>113.04595929755705</v>
+        <v>6.7906886039217517e-08</v>
       </c>
       <c r="F10" s="0">
-        <v>114.665558937436</v>
+        <v>9.2203601183279035e-08</v>
       </c>
       <c r="G10" s="0">
-        <v>105.50471422942582</v>
+        <v>2.8122664947167947e-08</v>
       </c>
       <c r="H10" s="0">
-        <v>135.24709922674776</v>
+        <v>7.49729227982085e-08</v>
       </c>
       <c r="I10" s="0">
-        <v>107.14717358580023</v>
+        <v>1.4813565568891205e-08</v>
       </c>
       <c r="J10" s="0">
-        <v>99.948654708966103</v>
+        <v>2.8635356273197701e-08</v>
       </c>
       <c r="K10" s="0">
-        <v>97.686463069026658</v>
+        <v>6.1307878319316733e-08</v>
       </c>
       <c r="L10" s="0">
-        <v>114.66965549405185</v>
+        <v>1.021389275739747e-07</v>
       </c>
       <c r="M10" s="0">
-        <v>139.25330066000532</v>
+        <v>3.0834296522909978e-07</v>
       </c>
       <c r="N10" s="0">
-        <v>95.580614235520841</v>
+        <v>1.4813565568891205e-08</v>
       </c>
       <c r="O10" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="0">
+        <v>5.3349629380884454e-08</v>
+      </c>
+      <c r="C11" s="0">
+        <v>3.5329669021828757e-08</v>
+      </c>
+      <c r="D11" s="0">
+        <v>4.4724440194143352e-08</v>
+      </c>
+      <c r="E11" s="0">
+        <v>3.8903287500371938e-08</v>
+      </c>
+      <c r="F11" s="0">
+        <v>9.3065982859046583e-08</v>
+      </c>
+      <c r="G11" s="0">
+        <v>9.0868122159901791e-08</v>
+      </c>
+      <c r="H11" s="0">
+        <v>2.5607016220511352e-07</v>
+      </c>
+      <c r="I11" s="0">
+        <v>1.9973339399201167e-08</v>
+      </c>
+      <c r="J11" s="0">
+        <v>2.1061521847084805e-08</v>
+      </c>
+      <c r="K11" s="0"/>
+      <c r="L11" s="0">
+        <v>7.2594017174175163e-08</v>
+      </c>
+      <c r="M11" s="0">
+        <v>2.5607016220511352e-07</v>
+      </c>
+      <c r="N11" s="0">
+        <v>1.9973339399201167e-08</v>
+      </c>
+      <c r="O11" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="0">
+        <v>6.5606898180254408e-08</v>
+      </c>
+      <c r="C12" s="0">
+        <v>3.3190026338171651e-07</v>
+      </c>
+      <c r="D12" s="0">
+        <v>5.5237101610116736e-08</v>
+      </c>
+      <c r="E12" s="0">
+        <v>9.7183713896999824e-09</v>
+      </c>
+      <c r="F12" s="0">
+        <v>2.4052101136523394e-07</v>
+      </c>
+      <c r="G12" s="0">
+        <v>1.945319078235319e-07</v>
+      </c>
+      <c r="H12" s="0">
+        <v>1.4378068671684107e-08</v>
+      </c>
+      <c r="I12" s="0">
+        <v>2.5754388194400651e-08</v>
+      </c>
+      <c r="J12" s="0">
+        <v>9.0300996170417994e-08</v>
+      </c>
+      <c r="K12" s="0">
+        <v>3.9651489009552329e-09</v>
+      </c>
+      <c r="L12" s="0">
+        <v>1.0319141556880114e-07</v>
+      </c>
+      <c r="M12" s="0">
+        <v>3.3190026338171651e-07</v>
+      </c>
+      <c r="N12" s="0">
+        <v>3.9651489009552329e-09</v>
+      </c>
+      <c r="O12" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="0">
+        <v>2.1201404686782527e-07</v>
+      </c>
+      <c r="C13" s="0">
+        <v>2.2852321581575321e-07</v>
+      </c>
+      <c r="D13" s="0">
+        <v>2.5923825996693556e-08</v>
+      </c>
+      <c r="E13" s="0">
+        <v>8.0851621714442529e-08</v>
+      </c>
+      <c r="F13" s="0">
+        <v>4.0418563351282929e-08</v>
+      </c>
+      <c r="G13" s="0">
+        <v>4.2502018689352948e-09</v>
+      </c>
+      <c r="H13" s="0">
+        <v>1.8400284442070721e-08</v>
+      </c>
+      <c r="I13" s="0">
+        <v>1.7537148913593337e-07</v>
+      </c>
+      <c r="J13" s="0">
+        <v>6.5126481161287059e-08</v>
+      </c>
+      <c r="K13" s="0">
+        <v>5.8292068796206277e-08</v>
+      </c>
+      <c r="L13" s="0">
+        <v>9.0917179915043029e-08</v>
+      </c>
+      <c r="M13" s="0">
+        <v>2.2852321581575321e-07</v>
+      </c>
+      <c r="N13" s="0">
+        <v>4.2502018689352948e-09</v>
+      </c>
+      <c r="O13" s="0" t="s">
         <v>22</v>
       </c>
     </row>
